--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484366_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484366_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.931</v>
+        <v>-0.1752</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3267</v>
+        <v>3.275</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.3957</v>
+        <v>-3.4502</v>
       </c>
       <c r="G2" t="n">
         <v>-3.5632</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1854</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4997</v>
+        <v>0.448</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3143</v>
+        <v>-0.3688</v>
       </c>
       <c r="V2" t="n">
         <v>1.5507</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2838</v>
+        <v>-0.4202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6845</v>
+        <v>0.2427</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4007</v>
+        <v>-0.6629</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2159</v>
+        <v>-0.9959</v>
       </c>
       <c r="H3" t="n">
-        <v>2.12</v>
+        <v>-0.7391</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9041</v>
+        <v>-0.2568</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9655</v>
+        <v>0.363</v>
       </c>
       <c r="K3" t="n">
-        <v>1.925</v>
+        <v>-0.3249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>0.6879</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7496</v>
+        <v>-1.3589</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1949</v>
+        <v>-0.4142</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9445</v>
+        <v>-0.9447</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5134</v>
+        <v>-0.401</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0594</v>
+        <v>-0.1203</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.546</v>
+        <v>-0.2807</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3695</v>
+        <v>-0.5735</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1508</v>
+        <v>-0.0639</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5203</v>
+        <v>-0.5097</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0669</v>
+        <v>1.2159</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4735</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5934</v>
+        <v>-0.9041</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2041</v>
+        <v>1.9655</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0435</v>
+        <v>1.925</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1607</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.271</v>
+        <v>-0.7496</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.517</v>
+        <v>0.1949</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.754</v>
+        <v>-0.9445</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9394</v>
+        <v>-0.3439</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9467</v>
+        <v>0.311</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0073</v>
+        <v>-0.6549</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8385</v>
+        <v>-1.1746</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1212</v>
+        <v>1.6452</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7174</v>
+        <v>-2.8199</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9959</v>
+        <v>-2.0669</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7391</v>
+        <v>-1.4735</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2568</v>
+        <v>-0.5934</v>
       </c>
       <c r="J5" t="n">
-        <v>0.363</v>
+        <v>1.2041</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3249</v>
+        <v>0.0435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6879</v>
+        <v>1.1607</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3589</v>
+        <v>-3.271</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4142</v>
+        <v>-1.517</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9447</v>
+        <v>-1.754</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8194</v>
+        <v>0.1342</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4842</v>
+        <v>0.4411</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3352</v>
+        <v>-0.3069</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2177</v>
+        <v>-1.5286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1528</v>
+        <v>0.5772</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3705</v>
+        <v>-2.1058</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9061</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1162</v>
+        <v>-0.4272</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8335</v>
+        <v>-0.4092</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7173</v>
+        <v>-0.0181</v>
       </c>
       <c r="V6" t="n">
         <v>0.6093</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9676</v>
+        <v>-2.1015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7955</v>
+        <v>0.5527</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7632</v>
+        <v>-2.6542</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6465</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2296</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4679</v>
+        <v>0.2251</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2383</v>
+        <v>-0.1294</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3321</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.043</v>
+        <v>-2.2512</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3012</v>
+        <v>-1.8362</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7419</v>
+        <v>-0.415</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2487</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3916</v>
+        <v>-0.5998</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5309</v>
+        <v>-0.0659</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8607</v>
+        <v>-0.5339</v>
       </c>
       <c r="V8" t="n">
         <v>0.9414</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1259</v>
+        <v>-2.8886</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3094</v>
+        <v>-2.2083</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8165</v>
+        <v>-0.6803</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4705</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.542</v>
+        <v>-0.3047</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1789</v>
+        <v>-0.0427</v>
       </c>
       <c r="V9" t="n">
         <v>0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5567</v>
+        <v>-4.3328</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2345</v>
+        <v>-1.174</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3222</v>
+        <v>-3.1587</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1462</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1566</v>
+        <v>-0.9327</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0522</v>
+        <v>0.0083</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1044</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3211</v>
+        <v>-5.6188</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5649</v>
+        <v>-1.9988</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7562</v>
+        <v>-3.62</v>
       </c>
       <c r="G11" t="n">
         <v>-5.9138</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8213</v>
+        <v>-1.119</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8335</v>
+        <v>-0.2674</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9878</v>
+        <v>-0.8516</v>
       </c>
       <c r="V11" t="n">
         <v>1.2186</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0446</v>
+        <v>-6.5174</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3485</v>
+        <v>-4.9846</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6961</v>
+        <v>-1.5327</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0834</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7659</v>
+        <v>-0.2386</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5309</v>
+        <v>-0.1671</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.235</v>
+        <v>-0.0716</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.714</v>
+        <v>-8.796200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.735</v>
+        <v>-5.9261</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.979</v>
+        <v>-2.8701</v>
       </c>
       <c r="G13" t="n">
         <v>-7.2885</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8395</v>
+        <v>-0.9216</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8941</v>
+        <v>-0.0851</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9454</v>
+        <v>-0.8365</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.9838</v>
+        <v>-36.3786</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.5044</v>
+        <v>-11.8991</v>
       </c>
       <c r="F14" t="n">
-        <v>-24.4797</v>
+        <v>-24.4795</v>
       </c>
       <c r="G14" t="n">
         <v>-34.1138</v>
@@ -1537,7 +1537,7 @@
         <v>-22.9362</v>
       </c>
       <c r="P14" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.6506</v>
@@ -1546,16 +1546,16 @@
         <v>14.6508</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.584700000000001</v>
+        <v>-4.9794</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5487000000000003</v>
+        <v>0.05650000000000004</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.036</v>
+        <v>-5.0361</v>
       </c>
       <c r="V14" t="n">
-        <v>2.714399999999999</v>
+        <v>2.7144</v>
       </c>
       <c r="W14" t="n">
         <v>2.4949</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.415900000000001</v>
+        <v>9.9937</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9556</v>
+        <v>8.103300000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4603</v>
+        <v>1.8903</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6308</v>
+        <v>10.3073</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1801</v>
+        <v>1.3518</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4506</v>
+        <v>8.9556</v>
       </c>
       <c r="J15" t="n">
-        <v>5.0327</v>
+        <v>9.3881</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6603</v>
+        <v>1.7805</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3725</v>
+        <v>7.6076</v>
       </c>
       <c r="M15" t="n">
-        <v>1.598</v>
+        <v>0.9193</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5199</v>
+        <v>-0.4287</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0782</v>
+        <v>1.348</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8632</v>
+        <v>0.663</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4819</v>
+        <v>0.864</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3814</v>
+        <v>-0.201</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2735</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.099</v>
+        <v>7.6408</v>
       </c>
       <c r="E16" t="n">
-        <v>7.6989</v>
+        <v>4.9445</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4001</v>
+        <v>2.6963</v>
       </c>
       <c r="G16" t="n">
-        <v>10.3073</v>
+        <v>6.6308</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3518</v>
+        <v>2.1801</v>
       </c>
       <c r="I16" t="n">
-        <v>8.9556</v>
+        <v>4.4506</v>
       </c>
       <c r="J16" t="n">
-        <v>9.3881</v>
+        <v>5.0327</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7805</v>
+        <v>1.6603</v>
       </c>
       <c r="L16" t="n">
-        <v>7.6076</v>
+        <v>3.3725</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9193</v>
+        <v>1.598</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4287</v>
+        <v>0.5199</v>
       </c>
       <c r="O16" t="n">
-        <v>1.348</v>
+        <v>1.0782</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2317</v>
+        <v>2.0881</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4596</v>
+        <v>1.4707</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6912</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2735</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0109</v>
+        <v>5.5394</v>
       </c>
       <c r="E17" t="n">
-        <v>6.298</v>
+        <v>5.4941</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.287</v>
+        <v>0.0453</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3144</v>
+        <v>3.8777</v>
       </c>
       <c r="H17" t="n">
-        <v>3.195</v>
+        <v>0.2888</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1194</v>
+        <v>3.5888</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3383</v>
+        <v>5.7155</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2745</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0638</v>
+        <v>4.9378</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0239</v>
+        <v>-1.8379</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0795</v>
+        <v>-0.4889</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9443</v>
+        <v>-1.349</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0008</v>
+        <v>0.099</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6592</v>
+        <v>-0.2214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3416</v>
+        <v>0.3205</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2841</v>
+        <v>5.0529</v>
       </c>
       <c r="E18" t="n">
-        <v>5.2918</v>
+        <v>5.2868</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0078</v>
+        <v>-0.2339</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8777</v>
+        <v>4.3144</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2888</v>
+        <v>3.195</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5888</v>
+        <v>1.1194</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7155</v>
+        <v>5.3383</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7776999999999999</v>
+        <v>3.2745</v>
       </c>
       <c r="L18" t="n">
-        <v>4.9378</v>
+        <v>2.0638</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8379</v>
+        <v>-1.0239</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4889</v>
+        <v>-0.0795</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.349</v>
+        <v>-0.9443</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1563</v>
+        <v>1.0428</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4237</v>
+        <v>0.648</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2673</v>
+        <v>0.3948</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.7768</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.9664</v>
+        <v>4.3557</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4379</v>
+        <v>2.2357</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5285</v>
+        <v>2.12</v>
       </c>
       <c r="G19" t="n">
         <v>2.9306</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2312</v>
+        <v>1.6204</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1337</v>
+        <v>0.9314</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0975</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.4515</v>
+        <v>4.2261</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4773</v>
+        <v>1.8706</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9742</v>
+        <v>2.3555</v>
       </c>
       <c r="G20" t="n">
         <v>2.761</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4951</v>
+        <v>1.2697</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7472</v>
+        <v>1.1405</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2521</v>
+        <v>0.1292</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3566</v>
+        <v>1.2135</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7582</v>
+        <v>-0.2526</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1148</v>
+        <v>1.4661</v>
       </c>
       <c r="G21" t="n">
         <v>1.2458</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.28</v>
+        <v>-0.423</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.3417</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4326</v>
+        <v>-0.0813</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3102</v>
+        <v>0.5928</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2666</v>
+        <v>-1.0644</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5768</v>
+        <v>1.6571</v>
       </c>
       <c r="G22" t="n">
         <v>-0.028</v>
@@ -2170,13 +2170,13 @@
         <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7985</v>
+        <v>-0.5159</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4842</v>
+        <v>-0.282</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3143</v>
+        <v>-0.234</v>
       </c>
       <c r="V22" t="n">
         <v>0.9414</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0406</v>
+        <v>0.4774</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8224</v>
+        <v>-1.507</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7818000000000001</v>
+        <v>1.9844</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5911</v>
+        <v>1.6654</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3083</v>
+        <v>-0.0745</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2829</v>
+        <v>1.7398</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8806</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.055</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2833</v>
+        <v>0.7965</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2895</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2891</v>
+        <v>-0.0194</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0004</v>
+        <v>0.9433</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R23" t="n">
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0457</v>
+        <v>0.5702</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2504</v>
+        <v>0.8771</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2961</v>
+        <v>-0.3069</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.662</v>
+        <v>0.1007</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5734</v>
+        <v>-0.9235</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2354</v>
+        <v>1.0242</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8439</v>
+        <v>0.5911</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7744</v>
+        <v>0.3083</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9305</v>
+        <v>0.2829</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5423</v>
+        <v>0.8806</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7191</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.2833</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6984</v>
+        <v>-0.2895</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0553</v>
+        <v>-0.2891</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7536</v>
+        <v>-0.0004</v>
       </c>
       <c r="P24" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2091</v>
+        <v>0.0956</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6052</v>
+        <v>0.1493</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3961</v>
+        <v>-0.0537</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0304</v>
+        <v>-0.0216</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.417</v>
+        <v>1.079</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3866</v>
+        <v>-1.1006</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6654</v>
+        <v>0.8439</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0745</v>
+        <v>1.7744</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7398</v>
+        <v>-0.9305</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7413999999999999</v>
+        <v>2.5423</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.055</v>
+        <v>1.7191</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7965</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9239000000000001</v>
+        <v>-1.6984</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0194</v>
+        <v>0.0553</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9433</v>
+        <v>-1.7536</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9377</v>
+        <v>0.4313</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.033</v>
+        <v>-0.0997</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9046999999999999</v>
+        <v>0.5309</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.1776</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9891</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1886</v>
+        <v>-0.0524</v>
       </c>
       <c r="G26" t="n">
         <v>-1.0263</v>
@@ -2482,13 +2482,13 @@
         <v>0.1953</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3466</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3026</v>
+        <v>-0.1004</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.044</v>
+        <v>0.0921</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>36.984</v>
+        <v>38.33220000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>24.4796</v>
+        <v>24.4797</v>
       </c>
       <c r="F27" t="n">
-        <v>12.5043</v>
+        <v>13.8523</v>
       </c>
       <c r="G27" t="n">
         <v>34.11369999999999</v>
@@ -2542,7 +2542,7 @@
         <v>22.9362</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2003</v>
+        <v>-0.2002999999999998</v>
       </c>
       <c r="N27" t="n">
         <v>1.1541</v>
@@ -2560,13 +2560,13 @@
         <v>14.6507</v>
       </c>
       <c r="S27" t="n">
-        <v>5.5847</v>
+        <v>6.933</v>
       </c>
       <c r="T27" t="n">
-        <v>5.036</v>
+        <v>5.035800000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5488999999999998</v>
+        <v>1.897</v>
       </c>
       <c r="V27" t="n">
         <v>-2.7145</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484366_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484366_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -565,67 +570,72 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1752</v>
+        <v>0.607</v>
       </c>
       <c r="E2" t="n">
-        <v>3.275</v>
+        <v>0.607</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.4502</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.5632</v>
+        <v>0.607</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0942</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.469</v>
+        <v>0.607</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9405</v>
+        <v>0.607</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1716</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7688</v>
+        <v>0.607</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.5036</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2658</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.2379</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3688</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -643,58 +653,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4202</v>
+        <v>0.607</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2427</v>
+        <v>0.607</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6629</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9959</v>
+        <v>0.607</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7391</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2568</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="n">
-        <v>0.363</v>
+        <v>0.607</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3249</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6879</v>
+        <v>0.607</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3589</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4142</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9447</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.401</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1203</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2807</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1746</v>
+        <v>-0.7822</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6452</v>
+        <v>2.668</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8199</v>
+        <v>-3.4502</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0669</v>
+        <v>-4.1702</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4735</v>
+        <v>-1.0942</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5934</v>
+        <v>-3.076</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2041</v>
+        <v>1.3335</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0435</v>
+        <v>1.1716</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1607</v>
+        <v>0.1619</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.271</v>
+        <v>-5.5036</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.517</v>
+        <v>-2.2658</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.754</v>
+        <v>-3.2379</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1342</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4411</v>
+        <v>0.448</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3069</v>
+        <v>-0.3688</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>1.5507</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. BALLUS TORRAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5286</v>
+        <v>-1.0272</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5772</v>
+        <v>-0.3643</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1058</v>
+        <v>-0.6629</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9061</v>
+        <v>-1.6029</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.408</v>
+        <v>-0.7391</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.498</v>
+        <v>-0.8638</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6858</v>
+        <v>-0.244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3505</v>
+        <v>-0.3249</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3354</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5919</v>
+        <v>-1.3589</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7585</v>
+        <v>-0.4142</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.8334</v>
+        <v>-0.9447</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4272</v>
+        <v>-0.401</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4092</v>
+        <v>-0.1203</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0181</v>
+        <v>-0.2807</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1015</v>
+        <v>-1.1746</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5527</v>
+        <v>1.6452</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6542</v>
+        <v>-2.8199</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6465</v>
+        <v>-2.0669</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0241</v>
+        <v>-1.4735</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6705</v>
+        <v>-0.5934</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3592</v>
+        <v>1.2041</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3315</v>
+        <v>0.0435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0276</v>
+        <v>1.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.0057</v>
+        <v>-3.271</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3075</v>
+        <v>-1.517</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6982</v>
+        <v>-1.754</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1342</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2251</v>
+        <v>0.4411</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1294</v>
+        <v>-0.3069</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3321</v>
+        <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2512</v>
+        <v>-1.5286</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8362</v>
+        <v>0.5772</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.415</v>
+        <v>-2.1058</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2487</v>
+        <v>-1.9061</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9496</v>
+        <v>-0.408</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7009</v>
+        <v>-1.498</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8594</v>
+        <v>1.6858</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0563</v>
+        <v>0.3505</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9157</v>
+        <v>1.3354</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1081</v>
+        <v>-3.5919</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8933</v>
+        <v>-0.7585</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2148</v>
+        <v>-2.8334</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5998</v>
+        <v>-0.4272</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0659</v>
+        <v>-0.4092</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5339</v>
+        <v>-0.0181</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9414</v>
+        <v>0.6093</v>
       </c>
       <c r="W8" t="n">
         <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8886</v>
+        <v>-2.1015</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2083</v>
+        <v>0.5527</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6803</v>
+        <v>-2.6542</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4705</v>
+        <v>-2.6465</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0115</v>
+        <v>0.0241</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4589</v>
+        <v>-2.6705</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2468</v>
+        <v>1.3592</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3277</v>
+        <v>1.3315</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>0.0276</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2237</v>
+        <v>-4.0057</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6838</v>
+        <v>-1.3075</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5399</v>
+        <v>-2.6982</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3047</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.262</v>
+        <v>0.2251</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0427</v>
+        <v>-0.1294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3328</v>
+        <v>-2.2512</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.174</v>
+        <v>-1.8362</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1587</v>
+        <v>-0.415</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1462</v>
+        <v>-0.2487</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2684</v>
+        <v>-0.9496</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4145</v>
+        <v>0.7009</v>
       </c>
       <c r="J10" t="n">
-        <v>0.771</v>
+        <v>1.8594</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7572</v>
+        <v>-0.0563</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0138</v>
+        <v>1.9157</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9172</v>
+        <v>-2.1081</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4889</v>
+        <v>-0.8933</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4283</v>
+        <v>-1.2148</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9327</v>
+        <v>-0.5998</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0083</v>
+        <v>-0.0659</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.5339</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6188</v>
+        <v>-2.8886</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9988</v>
+        <v>-2.2083</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.62</v>
+        <v>-0.6803</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.9138</v>
+        <v>-2.4705</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9491</v>
+        <v>-2.0115</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9647</v>
+        <v>-0.4589</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9733</v>
+        <v>-1.2468</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5718</v>
+        <v>-1.3277</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4015</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.9405</v>
+        <v>-1.2237</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3773</v>
+        <v>-0.6838</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5632</v>
+        <v>-0.5399</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.119</v>
+        <v>-0.3047</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2674</v>
+        <v>-0.262</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8516</v>
+        <v>-0.0427</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5174</v>
+        <v>-4.3328</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9846</v>
+        <v>-1.174</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5327</v>
+        <v>-3.1587</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.0834</v>
+        <v>-2.1462</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7928</v>
+        <v>0.2684</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2906</v>
+        <v>-2.4145</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8409</v>
+        <v>0.771</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8995</v>
+        <v>0.7572</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9414</v>
+        <v>0.0138</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2425</v>
+        <v>-2.9172</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8933</v>
+        <v>-0.4889</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3492</v>
+        <v>-2.4283</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2386</v>
+        <v>-0.9327</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1671</v>
+        <v>0.0083</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0716</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.796200000000001</v>
+        <v>-5.6188</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9261</v>
+        <v>-1.9988</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8701</v>
+        <v>-3.62</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.2885</v>
+        <v>-5.9138</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.526</v>
+        <v>-1.9491</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.7625</v>
+        <v>-3.9647</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.8875</v>
+        <v>-1.9733</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.5531</v>
+        <v>-0.5718</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3344</v>
+        <v>-1.4015</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.401</v>
+        <v>-3.9405</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9729</v>
+        <v>-1.3773</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.4281</v>
+        <v>-2.5632</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9216</v>
+        <v>-1.119</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0851</v>
+        <v>-0.2674</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8365</v>
+        <v>-0.8516</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,136 +1566,141 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.3786</v>
+        <v>-6.5174</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.8991</v>
+        <v>-4.9846</v>
       </c>
       <c r="F14" t="n">
-        <v>-24.4795</v>
+        <v>-1.5327</v>
       </c>
       <c r="G14" t="n">
-        <v>-34.1138</v>
+        <v>-6.0834</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.5313</v>
+        <v>-2.7928</v>
       </c>
       <c r="I14" t="n">
-        <v>-21.5821</v>
+        <v>-3.2906</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2000000000000002</v>
+        <v>-3.8409</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.154</v>
+        <v>-1.8995</v>
       </c>
       <c r="L14" t="n">
-        <v>1.354</v>
+        <v>-1.9414</v>
       </c>
       <c r="M14" t="n">
-        <v>-34.3137</v>
+        <v>-2.2425</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.3776</v>
+        <v>-0.8933</v>
       </c>
       <c r="O14" t="n">
-        <v>-22.9362</v>
+        <v>-1.3492</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.6506</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>14.6508</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.9794</v>
+        <v>-0.2386</v>
       </c>
       <c r="T14" t="n">
-        <v>0.05650000000000004</v>
+        <v>-0.1671</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.0361</v>
+        <v>-0.0716</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7144</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4949</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2196000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.9937</v>
+        <v>-8.796200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.103300000000001</v>
+        <v>-5.9261</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8903</v>
+        <v>-2.8701</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3073</v>
+        <v>-7.2885</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3518</v>
+        <v>-3.526</v>
       </c>
       <c r="I15" t="n">
-        <v>8.9556</v>
+        <v>-3.7625</v>
       </c>
       <c r="J15" t="n">
-        <v>9.3881</v>
+        <v>-3.8875</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7805</v>
+        <v>-2.5531</v>
       </c>
       <c r="L15" t="n">
-        <v>7.6076</v>
+        <v>-1.3344</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9193</v>
+        <v>-3.401</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4287</v>
+        <v>-0.9729</v>
       </c>
       <c r="O15" t="n">
-        <v>1.348</v>
+        <v>-2.4281</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.663</v>
+        <v>-0.9216</v>
       </c>
       <c r="T15" t="n">
-        <v>0.864</v>
+        <v>-0.0851</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.201</v>
+        <v>-0.8365</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,90 +1710,96 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.6408</v>
+        <v>-36.3786</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9445</v>
+        <v>-11.8991</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6963</v>
+        <v>-24.4795</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6308</v>
+        <v>-34.1138</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1801</v>
+        <v>-12.5313</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4506</v>
+        <v>-21.5821</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0327</v>
+        <v>0.200000000000002</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6603</v>
+        <v>-1.154000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3725</v>
+        <v>1.354099999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>1.598</v>
+        <v>-34.3137</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5199</v>
+        <v>-11.3776</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0782</v>
+        <v>-22.9362</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-14.6506</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>14.6508</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0881</v>
+        <v>-4.9794</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4707</v>
+        <v>0.05649999999999993</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6173999999999999</v>
+        <v>-5.0361</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2735</v>
+        <v>2.7144</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3869</v>
+        <v>2.4949</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8865</v>
-      </c>
+        <v>0.2196</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5394</v>
+        <v>9.9937</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4941</v>
+        <v>8.103300000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0453</v>
+        <v>1.8903</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8777</v>
+        <v>10.3073</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2888</v>
+        <v>1.3518</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5888</v>
+        <v>8.9556</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7155</v>
+        <v>9.3881</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.7805</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9378</v>
+        <v>7.6076</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8379</v>
+        <v>0.9193</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4889</v>
+        <v>-0.4287</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.349</v>
+        <v>1.348</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0.099</v>
+        <v>0.663</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2214</v>
+        <v>0.864</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3205</v>
+        <v>-0.201</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.0529</v>
+        <v>7.6408</v>
       </c>
       <c r="E18" t="n">
-        <v>5.2868</v>
+        <v>4.9445</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2339</v>
+        <v>2.6963</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3144</v>
+        <v>6.6308</v>
       </c>
       <c r="H18" t="n">
-        <v>3.195</v>
+        <v>2.1801</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1194</v>
+        <v>4.4506</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3383</v>
+        <v>5.0327</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2745</v>
+        <v>1.6603</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0638</v>
+        <v>3.3725</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0239</v>
+        <v>1.598</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0795</v>
+        <v>0.5199</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9443</v>
+        <v>1.0782</v>
       </c>
       <c r="P18" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0428</v>
+        <v>2.0881</v>
       </c>
       <c r="T18" t="n">
-        <v>0.648</v>
+        <v>1.4707</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3948</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4996</v>
+        <v>-1.2735</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>-0.3869</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7768</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.3557</v>
+        <v>5.5394</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2357</v>
+        <v>5.4941</v>
       </c>
       <c r="F19" t="n">
-        <v>2.12</v>
+        <v>0.0453</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9306</v>
+        <v>3.8777</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2448</v>
+        <v>0.2888</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6857</v>
+        <v>3.5888</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4763</v>
+        <v>5.7155</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9248</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5515</v>
+        <v>4.9378</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4543</v>
+        <v>-1.8379</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3201</v>
+        <v>-0.4889</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1342</v>
+        <v>-1.349</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6204</v>
+        <v>0.099</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9314</v>
+        <v>-0.2214</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.3205</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2261</v>
+        <v>5.0529</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8706</v>
+        <v>5.2868</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3555</v>
+        <v>-0.2339</v>
       </c>
       <c r="G20" t="n">
-        <v>2.761</v>
+        <v>4.3144</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5224</v>
+        <v>3.195</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2386</v>
+        <v>1.1194</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9021</v>
+        <v>5.3383</v>
       </c>
       <c r="K20" t="n">
-        <v>0.472</v>
+        <v>3.2745</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4301</v>
+        <v>2.0638</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8589</v>
+        <v>-1.0239</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0504</v>
+        <v>-0.0795</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8085</v>
+        <v>-0.9443</v>
       </c>
       <c r="P20" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2697</v>
+        <v>1.0428</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1405</v>
+        <v>0.648</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1292</v>
+        <v>0.3948</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.7768</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2135</v>
+        <v>4.3557</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2526</v>
+        <v>2.2357</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4661</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2458</v>
+        <v>2.9306</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9207</v>
+        <v>1.2448</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3251</v>
+        <v>1.6857</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0659</v>
+        <v>2.4763</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4707</v>
+        <v>0.9248</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5951</v>
+        <v>1.5515</v>
       </c>
       <c r="M21" t="n">
-        <v>0.18</v>
+        <v>0.4543</v>
       </c>
       <c r="N21" t="n">
-        <v>0.45</v>
+        <v>0.3201</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.27</v>
+        <v>0.1342</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.423</v>
+        <v>1.6204</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3417</v>
+        <v>0.9314</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0813</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5928</v>
+        <v>4.2261</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0644</v>
+        <v>1.8706</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6571</v>
+        <v>2.3555</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.028</v>
+        <v>2.761</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.5224</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0114</v>
+        <v>2.2386</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0829</v>
+        <v>1.9021</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3888</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4718</v>
+        <v>1.4301</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0549</v>
+        <v>0.8589</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5946</v>
+        <v>0.0504</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5397</v>
+        <v>0.8085</v>
       </c>
       <c r="P22" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5159</v>
+        <v>1.2697</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.282</v>
+        <v>1.1405</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.234</v>
+        <v>0.1292</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4774</v>
+        <v>2.7349</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.507</v>
+        <v>2.7349</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9844</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6654</v>
+        <v>2.7349</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0745</v>
+        <v>0.307</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7398</v>
+        <v>2.4279</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7413999999999999</v>
+        <v>2.7349</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.055</v>
+        <v>0.307</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7965</v>
+        <v>2.4279</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9239000000000001</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0194</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5702</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8771</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3069</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1007</v>
+        <v>0.5928</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9235</v>
+        <v>-1.0644</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0242</v>
+        <v>1.6571</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5911</v>
+        <v>-0.028</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3083</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2829</v>
+        <v>-1.0114</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8806</v>
+        <v>-0.0829</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.3888</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2833</v>
+        <v>-0.4718</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2895</v>
+        <v>0.0549</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2891</v>
+        <v>0.5946</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0004</v>
+        <v>-0.5397</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0956</v>
+        <v>-0.5159</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1493</v>
+        <v>-0.282</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0537</v>
+        <v>-0.234</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0216</v>
+        <v>0.4774</v>
       </c>
       <c r="E25" t="n">
-        <v>1.079</v>
+        <v>-1.507</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1006</v>
+        <v>1.9844</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8439</v>
+        <v>1.6654</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7744</v>
+        <v>-0.0745</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9305</v>
+        <v>1.7398</v>
       </c>
       <c r="J25" t="n">
-        <v>2.5423</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7191</v>
+        <v>-0.055</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.7965</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6984</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0553</v>
+        <v>-0.0194</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7536</v>
+        <v>0.9433</v>
       </c>
       <c r="P25" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4313</v>
+        <v>0.5702</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0997</v>
+        <v>0.8771</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5309</v>
+        <v>-0.3069</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>G. BAYO GARCIA</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,58 +2558,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8391999999999999</v>
+        <v>0.1007</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.9235</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0524</v>
+        <v>1.0242</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.0263</v>
+        <v>0.5911</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1637</v>
+        <v>0.3083</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8626</v>
+        <v>0.2829</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6865</v>
+        <v>0.8806</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6332</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0533</v>
+        <v>0.2833</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3399</v>
+        <v>-0.2895</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4694</v>
+        <v>-0.2891</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8093</v>
+        <v>-0.0004</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0956</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1004</v>
+        <v>0.1493</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0921</v>
+        <v>-0.0537</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2498,12 +2619,17 @@
       </c>
       <c r="X26" t="n">
         <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,68 +2641,318 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.1006</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.7744</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.9305</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.5423</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.7191</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.8231000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.6984</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.7536</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.0997</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.5309</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>G. BAYO GARCIA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.8391999999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.7868000000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.0524</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.0263</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.1637</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.8626</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.6865</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.6332</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.0533</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.3399</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.8093</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.1004</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S. COSTA I VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.5214</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-2.9875</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.4661</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-1.4891</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6137</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-2.1028</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-1.6691</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1.8328</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.423</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.3417</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.0813</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>play_by_play_2484366_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>38.33220000000001</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E30" t="n">
         <v>24.4797</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F30" t="n">
         <v>13.8523</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G30" t="n">
         <v>34.11369999999999</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H30" t="n">
         <v>12.5315</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I30" t="n">
         <v>21.582</v>
       </c>
-      <c r="J27" t="n">
-        <v>34.31379999999999</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J30" t="n">
+        <v>34.31369999999999</v>
+      </c>
+      <c r="K30" t="n">
         <v>11.3775</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L30" t="n">
         <v>22.9362</v>
       </c>
-      <c r="M27" t="n">
-        <v>-0.2002999999999998</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="M30" t="n">
+        <v>-0.2003</v>
+      </c>
+      <c r="N30" t="n">
         <v>1.1541</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O30" t="n">
         <v>-1.3541</v>
       </c>
-      <c r="P27" t="n">
-        <v>-0.0002000000000000057</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="P30" t="n">
+        <v>-0.0002000000000001445</v>
+      </c>
+      <c r="Q30" t="n">
         <v>-14.6508</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R30" t="n">
         <v>14.6507</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S30" t="n">
         <v>6.933</v>
       </c>
-      <c r="T27" t="n">
-        <v>5.035800000000001</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="T30" t="n">
+        <v>5.0358</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.897</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V30" t="n">
         <v>-2.7145</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W30" t="n">
         <v>-0.2194</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X30" t="n">
         <v>-2.495</v>
       </c>
+      <c r="Y30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
